--- a/research/CCC.NZ/Reports/CCC.NZ_DCF_Model.xlsx
+++ b/research/CCC.NZ/Reports/CCC.NZ_DCF_Model.xlsx
@@ -2574,9 +2574,10 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="9">
-        <f> Underlying/comparable OCF</f>
-        <v>0</v>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>= Underlying/comparable OCF</t>
+        </is>
       </c>
       <c r="B10" s="6">
         <v>-0.632</v>
@@ -2615,9 +2616,10 @@
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="9">
-        <f> Underlying/comparable FCF</f>
-        <v>0</v>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>= Underlying/comparable FCF</t>
+        </is>
       </c>
       <c r="B12" s="6">
         <v>-0.756</v>
